--- a/data/input/preparation/ai_results/coding_comparison_adidas.xlsx
+++ b/data/input/preparation/ai_results/coding_comparison_adidas.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -503,7 +503,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -535,7 +535,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -599,7 +599,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -759,7 +759,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>negative</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -919,7 +919,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1335,7 +1335,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1399,7 +1399,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1463,7 +1463,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1527,7 +1527,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1655,7 +1655,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1719,7 +1719,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>positive</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
